--- a/bills/huixinjiqiren/6486819279/7245cad451d2a4c1ec431882c82a535377c2a9e9001db1872bda3e78a0d6f36f/bill-current.xlsx
+++ b/bills/huixinjiqiren/6486819279/7245cad451d2a4c1ec431882c82a535377c2a9e9001db1872bda3e78a0d6f36f/bill-current.xlsx
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>125</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/6486819279/7245cad451d2a4c1ec431882c82a535377c2a9e9001db1872bda3e78a0d6f36f/bill-current.xlsx
+++ b/bills/huixinjiqiren/6486819279/7245cad451d2a4c1ec431882c82a535377c2a9e9001db1872bda3e78a0d6f36f/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 20:23:47</t>
+          <t>10/01 15:07:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111.11</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>111.11</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/6486819279/7245cad451d2a4c1ec431882c82a535377c2a9e9001db1872bda3e78a0d6f36f/bill-current.xlsx
+++ b/bills/huixinjiqiren/6486819279/7245cad451d2a4c1ec431882c82a535377c2a9e9001db1872bda3e78a0d6f36f/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/01 15:07:09</t>
+          <t>10/01 15:07:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>125</t>
         </is>
       </c>
     </row>
